--- a/salidas/empresas/CRM.xlsx
+++ b/salidas/empresas/CRM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.07025718688965</v>
+        <v>10.07025527954102</v>
       </c>
       <c r="C2" t="n">
         <v>10.26249980926514</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.549291610717773</v>
+        <v>8.549293518066406</v>
       </c>
       <c r="C3" t="n">
         <v>8.712499618530273</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>8.912360191345215</v>
+        <v>8.912362098693848</v>
       </c>
       <c r="C4" t="n">
         <v>9.082500457763672</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>8.598354339599609</v>
+        <v>8.598355293273926</v>
       </c>
       <c r="C5" t="n">
         <v>8.762499809265137</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>7.239300727844238</v>
+        <v>7.23930025100708</v>
       </c>
       <c r="C6" t="n">
         <v>7.377500057220459</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>6.540147304534912</v>
+        <v>6.540146827697754</v>
       </c>
       <c r="C7" t="n">
         <v>6.664999961853027</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>6.304643154144287</v>
+        <v>6.304644107818604</v>
       </c>
       <c r="C8" t="n">
         <v>6.425000190734863</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>8.458524703979492</v>
+        <v>8.458523750305176</v>
       </c>
       <c r="C9" t="n">
         <v>8.619999885559082</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>8.801968574523926</v>
+        <v>8.801969528198242</v>
       </c>
       <c r="C10" t="n">
         <v>8.970000267028809</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>9.572264671325684</v>
+        <v>9.572262763977051</v>
       </c>
       <c r="C11" t="n">
         <v>9.755000114440918</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>9.567358016967773</v>
+        <v>9.567356109619141</v>
       </c>
       <c r="C12" t="n">
         <v>9.75</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>8.941799163818359</v>
+        <v>8.941800117492676</v>
       </c>
       <c r="C13" t="n">
         <v>9.112500190734863</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.60750102996826</v>
+        <v>10.60750007629395</v>
       </c>
       <c r="C15" t="n">
         <v>10.8100004196167</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.50446701049805</v>
+        <v>10.50446605682373</v>
       </c>
       <c r="C16" t="n">
         <v>10.70499992370605</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>11.59122180938721</v>
+        <v>11.59121990203857</v>
       </c>
       <c r="C18" t="n">
         <v>11.8125</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.51427936553955</v>
+        <v>10.51428031921387</v>
       </c>
       <c r="C19" t="n">
         <v>10.71500015258789</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>9.533013343811035</v>
+        <v>9.533012390136719</v>
       </c>
       <c r="C20" t="n">
         <v>9.715000152587891</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>12.58966159820557</v>
+        <v>12.58966064453125</v>
       </c>
       <c r="C22" t="n">
         <v>12.82999992370605</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>13.82851123809814</v>
+        <v>13.82851028442383</v>
       </c>
       <c r="C23" t="n">
         <v>14.09249973297119</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>12.73439788818359</v>
+        <v>12.73439693450928</v>
       </c>
       <c r="C26" t="n">
         <v>12.97749996185303</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.65032291412354</v>
+        <v>14.65032196044922</v>
       </c>
       <c r="C27" t="n">
         <v>14.93000030517578</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>14.1964864730835</v>
+        <v>14.19648551940918</v>
       </c>
       <c r="C28" t="n">
         <v>14.46749973297119</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.73886108398438</v>
+        <v>17.73885726928711</v>
       </c>
       <c r="C30" t="n">
         <v>18.07749938964844</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.73796844482422</v>
+        <v>16.73797225952148</v>
       </c>
       <c r="C31" t="n">
         <v>17.0575008392334</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>15.64876174926758</v>
+        <v>15.64876079559326</v>
       </c>
       <c r="C32" t="n">
         <v>15.94750022888184</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.74264907836914</v>
+        <v>13.74265098571777</v>
       </c>
       <c r="C33" t="n">
         <v>14.00500011444092</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>11.87333679199219</v>
+        <v>11.87333583831787</v>
       </c>
       <c r="C34" t="n">
         <v>12.10000038146973</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.595008850097656</v>
+        <v>7.595009326934814</v>
       </c>
       <c r="C35" t="n">
         <v>7.739999771118164</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.852591514587402</v>
+        <v>7.852592468261719</v>
       </c>
       <c r="C37" t="n">
         <v>8.002499580383301</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.527882099151611</v>
+        <v>6.527881145477295</v>
       </c>
       <c r="C38" t="n">
         <v>6.652500152587891</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.868872165679932</v>
+        <v>6.86887264251709</v>
       </c>
       <c r="C39" t="n">
         <v>7</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.50201511383057</v>
+        <v>10.50201416015625</v>
       </c>
       <c r="C41" t="n">
         <v>10.70250034332275</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.309776306152344</v>
+        <v>9.309773445129395</v>
       </c>
       <c r="C42" t="n">
         <v>9.487500190734863</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>10.63203239440918</v>
+        <v>10.63203144073486</v>
       </c>
       <c r="C44" t="n">
         <v>10.83500003814697</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.72458457946777</v>
+        <v>12.72458362579346</v>
       </c>
       <c r="C45" t="n">
         <v>12.96749973297119</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.96588897705078</v>
+        <v>13.96588802337646</v>
       </c>
       <c r="C46" t="n">
         <v>14.23250007629395</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.92173194885254</v>
+        <v>13.92173004150391</v>
       </c>
       <c r="C47" t="n">
         <v>14.1875</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.37646102905273</v>
+        <v>15.3764591217041</v>
       </c>
       <c r="C48" t="n">
         <v>15.67000007629395</v>
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.58988475799561</v>
+        <v>15.58988761901855</v>
       </c>
       <c r="C50" t="n">
         <v>15.88749980926514</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>18.26383972167969</v>
+        <v>18.26383590698242</v>
       </c>
       <c r="C52" t="n">
         <v>18.61249923706055</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>20.99912643432617</v>
+        <v>20.99912071228027</v>
       </c>
       <c r="C53" t="n">
         <v>21.39999961853027</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>26.95541381835938</v>
+        <v>26.95541572570801</v>
       </c>
       <c r="C57" t="n">
         <v>27.46999931335449</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.42642784118652</v>
+        <v>27.42642402648926</v>
       </c>
       <c r="C58" t="n">
         <v>27.95000076293945</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>28.47392463684082</v>
+        <v>28.47393035888672</v>
       </c>
       <c r="C59" t="n">
         <v>29.01749992370605</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>34.15301132202148</v>
+        <v>34.15301895141602</v>
       </c>
       <c r="C60" t="n">
         <v>34.80500030517578</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>31.68022346496582</v>
+        <v>31.68021583557129</v>
       </c>
       <c r="C62" t="n">
         <v>32.28499984741211</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>32.44806289672852</v>
+        <v>32.44805908203125</v>
       </c>
       <c r="C63" t="n">
         <v>33.06750106811523</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>32.76942825317383</v>
+        <v>32.76942443847656</v>
       </c>
       <c r="C64" t="n">
         <v>33.39500045776367</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>34.00091552734375</v>
+        <v>34.00092315673828</v>
       </c>
       <c r="C65" t="n">
         <v>34.65000152587891</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>37.35194396972656</v>
+        <v>37.35193634033203</v>
       </c>
       <c r="C66" t="n">
         <v>38.06499862670898</v>
@@ -1861,7 +1873,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1890,7 +1902,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.58454704284668</v>
+        <v>31.58453750610352</v>
       </c>
       <c r="C69" t="n">
         <v>32.1875</v>
@@ -1948,7 +1960,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.66885375976562</v>
+        <v>32.66884231567383</v>
       </c>
       <c r="C71" t="n">
         <v>33.29249954223633</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>29.0504207611084</v>
+        <v>29.05042266845703</v>
       </c>
       <c r="C72" t="n">
         <v>29.60499954223633</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>24.88984489440918</v>
+        <v>24.88984680175781</v>
       </c>
       <c r="C73" t="n">
         <v>25.36499977111816</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.65300941467285</v>
+        <v>28.65301132202148</v>
       </c>
       <c r="C74" t="n">
         <v>29.20000076293945</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>35.11956405639648</v>
+        <v>35.11955261230469</v>
       </c>
       <c r="C75" t="n">
         <v>35.79000091552734</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.90391159057617</v>
+        <v>37.90390014648438</v>
       </c>
       <c r="C76" t="n">
         <v>38.62749862670898</v>
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>38.20319747924805</v>
+        <v>38.20319366455078</v>
       </c>
       <c r="C77" t="n">
         <v>38.93249893188477</v>
@@ -2176,11 +2188,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>34.00581741333008</v>
+        <v>34.00582504272461</v>
       </c>
       <c r="C78" t="n">
         <v>34.65499877929688</v>
@@ -2203,11 +2215,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>33.91750335693359</v>
+        <v>33.91751098632812</v>
       </c>
       <c r="C79" t="n">
         <v>34.56499862670898</v>
@@ -2230,11 +2242,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>30.50760269165039</v>
+        <v>30.50760459899902</v>
       </c>
       <c r="C80" t="n">
         <v>31.09000015258789</v>
@@ -2257,11 +2269,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>35.6151008605957</v>
+        <v>35.61509704589844</v>
       </c>
       <c r="C81" t="n">
         <v>36.29499816894531</v>
@@ -2284,11 +2296,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>37.45742797851562</v>
+        <v>37.45743560791016</v>
       </c>
       <c r="C82" t="n">
         <v>38.17250061035156</v>
@@ -2311,7 +2323,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2338,11 +2350,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>38.67911148071289</v>
+        <v>38.67910385131836</v>
       </c>
       <c r="C84" t="n">
         <v>39.41749954223633</v>
@@ -2365,7 +2377,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2392,7 +2404,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2419,11 +2431,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.51251983642578</v>
+        <v>41.51251220703125</v>
       </c>
       <c r="C87" t="n">
         <v>42.30500030517578</v>
@@ -2446,11 +2458,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.87001419067383</v>
+        <v>43.87001037597656</v>
       </c>
       <c r="C88" t="n">
         <v>44.70750045776367</v>
@@ -2473,11 +2485,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>40.33989715576172</v>
+        <v>40.33990097045898</v>
       </c>
       <c r="C89" t="n">
         <v>41.11000061035156</v>
@@ -2500,7 +2512,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2527,11 +2539,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>37.46478652954102</v>
+        <v>37.46479034423828</v>
       </c>
       <c r="C91" t="n">
         <v>38.18000030517578</v>
@@ -2554,11 +2566,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.93045043945312</v>
+        <v>42.93044662475586</v>
       </c>
       <c r="C92" t="n">
         <v>43.75</v>
@@ -2581,11 +2593,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.20967102050781</v>
+        <v>48.20966339111328</v>
       </c>
       <c r="C93" t="n">
         <v>49.13000106811523</v>
@@ -2608,11 +2620,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.93759155273438</v>
+        <v>50.93758773803711</v>
       </c>
       <c r="C94" t="n">
         <v>51.90999984741211</v>
@@ -2635,11 +2647,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.36043167114258</v>
+        <v>52.36042404174805</v>
       </c>
       <c r="C95" t="n">
         <v>53.36000061035156</v>
@@ -2662,11 +2674,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.11421966552734</v>
+        <v>51.11421585083008</v>
       </c>
       <c r="C96" t="n">
         <v>52.09000015258789</v>
@@ -2689,7 +2701,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2716,7 +2728,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>61.2016487121582</v>
+        <v>61.20164489746094</v>
       </c>
       <c r="C99" t="n">
         <v>62.36999893188477</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.02055358886719</v>
+        <v>56.02054977416992</v>
       </c>
       <c r="C100" t="n">
         <v>57.09000015258789</v>
@@ -2797,11 +2809,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>50.68245697021484</v>
+        <v>50.68246078491211</v>
       </c>
       <c r="C101" t="n">
         <v>51.65000152587891</v>
@@ -2824,11 +2836,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>51.64410781860352</v>
+        <v>51.64410400390625</v>
       </c>
       <c r="C102" t="n">
         <v>52.63000106811523</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.99200820922852</v>
+        <v>56.99200439453125</v>
       </c>
       <c r="C103" t="n">
         <v>58.08000183105469</v>
@@ -2878,11 +2890,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>53.2337646484375</v>
+        <v>53.23375701904297</v>
       </c>
       <c r="C104" t="n">
         <v>54.25</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>57.98308944702148</v>
+        <v>57.98309326171875</v>
       </c>
       <c r="C105" t="n">
         <v>59.09000015258789</v>
@@ -2932,7 +2944,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -2959,7 +2971,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2986,11 +2998,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>58.74847412109375</v>
+        <v>58.74847793579102</v>
       </c>
       <c r="C108" t="n">
         <v>59.86999893188477</v>
@@ -3013,7 +3025,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3040,11 +3052,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>55.39253997802734</v>
+        <v>55.39255142211914</v>
       </c>
       <c r="C110" t="n">
         <v>56.45000076293945</v>
@@ -3067,7 +3079,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>65.55847930908203</v>
+        <v>65.55846405029297</v>
       </c>
       <c r="C112" t="n">
         <v>66.80999755859375</v>
@@ -3121,7 +3133,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3148,7 +3160,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3175,11 +3187,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>68.32565307617188</v>
+        <v>68.32564544677734</v>
       </c>
       <c r="C115" t="n">
         <v>69.62999725341797</v>
@@ -3202,7 +3214,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3229,11 +3241,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>68.06070709228516</v>
+        <v>68.06069946289062</v>
       </c>
       <c r="C117" t="n">
         <v>69.36000061035156</v>
@@ -3256,11 +3268,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>68.12940216064453</v>
+        <v>68.12940979003906</v>
       </c>
       <c r="C118" t="n">
         <v>69.43000030517578</v>
@@ -3283,11 +3295,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>76.25428771972656</v>
+        <v>76.25429534912109</v>
       </c>
       <c r="C119" t="n">
         <v>77.70999908447266</v>
@@ -3310,11 +3322,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>78.19719696044922</v>
+        <v>78.19721221923828</v>
       </c>
       <c r="C120" t="n">
         <v>79.69000244140625</v>
@@ -3337,11 +3349,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>76.93136596679688</v>
+        <v>76.93137359619141</v>
       </c>
       <c r="C121" t="n">
         <v>78.40000152587891</v>
@@ -3364,11 +3376,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>66.78504180908203</v>
+        <v>66.78505706787109</v>
       </c>
       <c r="C122" t="n">
         <v>68.05999755859375</v>
@@ -3391,7 +3403,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3418,11 +3430,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>72.44697570800781</v>
+        <v>72.44696807861328</v>
       </c>
       <c r="C124" t="n">
         <v>73.83000183105469</v>
@@ -3445,7 +3457,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3472,11 +3484,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>82.14190673828125</v>
+        <v>82.14189147949219</v>
       </c>
       <c r="C126" t="n">
         <v>83.70999908447266</v>
@@ -3499,11 +3511,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>77.92244720458984</v>
+        <v>77.92245483398438</v>
       </c>
       <c r="C127" t="n">
         <v>79.41000366210938</v>
@@ -3526,11 +3538,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>80.26767730712891</v>
+        <v>80.26766967773438</v>
       </c>
       <c r="C128" t="n">
         <v>81.80000305175781</v>
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3580,11 +3592,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>69.99381256103516</v>
+        <v>69.99378967285156</v>
       </c>
       <c r="C130" t="n">
         <v>71.33000183105469</v>
@@ -3609,7 +3621,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3638,11 +3650,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>70.6512451171875</v>
+        <v>70.65126037597656</v>
       </c>
       <c r="C132" t="n">
         <v>72</v>
@@ -3667,7 +3679,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3696,7 +3708,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3725,11 +3737,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>79.82610321044922</v>
+        <v>79.82611083984375</v>
       </c>
       <c r="C135" t="n">
         <v>81.34999847412109</v>
@@ -3754,11 +3766,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>80.94474029541016</v>
+        <v>80.94473266601562</v>
       </c>
       <c r="C136" t="n">
         <v>82.48999786376953</v>
@@ -3783,11 +3795,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>84.50674438476562</v>
+        <v>84.50675201416016</v>
       </c>
       <c r="C137" t="n">
         <v>86.12000274658203</v>
@@ -3812,11 +3824,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>87.96080017089844</v>
+        <v>87.96080780029297</v>
       </c>
       <c r="C138" t="n">
         <v>89.63999938964844</v>
@@ -3841,7 +3853,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3870,11 +3882,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>89.09909057617188</v>
+        <v>89.09907531738281</v>
       </c>
       <c r="C140" t="n">
         <v>90.80000305175781</v>
@@ -3899,11 +3911,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>93.70121002197266</v>
+        <v>93.70122528076172</v>
       </c>
       <c r="C141" t="n">
         <v>95.48999786376953</v>
@@ -3926,7 +3938,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>100.4228897094727</v>
+        <v>100.4228973388672</v>
       </c>
       <c r="C143" t="n">
         <v>102.3399963378906</v>
@@ -3980,11 +3992,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>102.3658142089844</v>
+        <v>102.3658218383789</v>
       </c>
       <c r="C144" t="n">
         <v>104.3199996948242</v>
@@ -4009,7 +4021,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4038,7 +4050,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4067,11 +4079,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>114.0723342895508</v>
+        <v>114.0723419189453</v>
       </c>
       <c r="C147" t="n">
         <v>116.25</v>
@@ -4096,7 +4108,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4125,11 +4137,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>118.7235488891602</v>
+        <v>118.7235412597656</v>
       </c>
       <c r="C149" t="n">
         <v>120.9899978637695</v>
@@ -4154,11 +4166,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>126.9073104858398</v>
+        <v>126.9073028564453</v>
       </c>
       <c r="C150" t="n">
         <v>129.3300018310547</v>
@@ -4183,11 +4195,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>133.8448486328125</v>
+        <v>133.8448638916016</v>
       </c>
       <c r="C151" t="n">
         <v>136.3999938964844</v>
@@ -4212,11 +4224,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>134.5808410644531</v>
+        <v>134.5808258056641</v>
       </c>
       <c r="C152" t="n">
         <v>137.1499938964844</v>
@@ -4241,7 +4253,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4270,11 +4282,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>156.0509338378906</v>
+        <v>156.0509490966797</v>
       </c>
       <c r="C154" t="n">
         <v>159.0299987792969</v>
@@ -4299,7 +4311,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4328,11 +4340,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>140.0857238769531</v>
+        <v>140.0857543945312</v>
       </c>
       <c r="C156" t="n">
         <v>142.7599945068359</v>
@@ -4357,7 +4369,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4386,7 +4398,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4415,11 +4427,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>160.5844116210938</v>
+        <v>160.5843963623047</v>
       </c>
       <c r="C159" t="n">
         <v>163.6499938964844</v>
@@ -4444,11 +4456,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>155.4033050537109</v>
+        <v>155.4033355712891</v>
       </c>
       <c r="C160" t="n">
         <v>158.3699951171875</v>
@@ -4473,7 +4485,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4502,11 +4514,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>148.5737152099609</v>
+        <v>148.5736999511719</v>
       </c>
       <c r="C162" t="n">
         <v>151.4100036621094</v>
@@ -4531,11 +4543,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>148.8877105712891</v>
+        <v>148.8876953125</v>
       </c>
       <c r="C163" t="n">
         <v>151.7299957275391</v>
@@ -4560,11 +4572,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>151.6058349609375</v>
+        <v>151.6058044433594</v>
       </c>
       <c r="C164" t="n">
         <v>154.5</v>
@@ -4589,11 +4601,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>153.1464385986328</v>
+        <v>153.1463928222656</v>
       </c>
       <c r="C165" t="n">
         <v>156.0700073242188</v>
@@ -4618,11 +4630,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>145.6593627929688</v>
+        <v>145.6593475341797</v>
       </c>
       <c r="C166" t="n">
         <v>148.4400024414062</v>
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4676,7 +4688,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4705,11 +4717,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>159.5933227539062</v>
+        <v>159.5933074951172</v>
       </c>
       <c r="C169" t="n">
         <v>162.6399993896484</v>
@@ -4734,7 +4746,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4763,11 +4775,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>167.2079772949219</v>
+        <v>167.2079315185547</v>
       </c>
       <c r="C171" t="n">
         <v>170.3999938964844</v>
@@ -4792,11 +4804,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>141.2828826904297</v>
+        <v>141.2828674316406</v>
       </c>
       <c r="C172" t="n">
         <v>143.9799957275391</v>
@@ -4821,11 +4833,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>158.9162292480469</v>
+        <v>158.916259765625</v>
       </c>
       <c r="C173" t="n">
         <v>161.9499969482422</v>
@@ -4850,11 +4862,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>171.5157165527344</v>
+        <v>171.5157318115234</v>
       </c>
       <c r="C174" t="n">
         <v>174.7899932861328</v>
@@ -4879,11 +4891,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>183.8208160400391</v>
+        <v>183.8208312988281</v>
       </c>
       <c r="C175" t="n">
         <v>187.3300018310547</v>
@@ -4906,7 +4918,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4933,11 +4945,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>267.5425415039062</v>
+        <v>267.5425109863281</v>
       </c>
       <c r="C177" t="n">
         <v>272.6499938964844</v>
@@ -4962,11 +4974,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>246.6121368408203</v>
+        <v>246.6121215820312</v>
       </c>
       <c r="C178" t="n">
         <v>251.3200073242188</v>
@@ -4991,7 +5003,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5020,11 +5032,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>241.1955108642578</v>
+        <v>241.1955261230469</v>
       </c>
       <c r="C180" t="n">
         <v>245.8000030517578</v>
@@ -5049,7 +5061,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5078,11 +5090,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.3346557617188</v>
+        <v>221.3347015380859</v>
       </c>
       <c r="C182" t="n">
         <v>225.5599975585938</v>
@@ -5107,7 +5119,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5136,11 +5148,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>207.9011077880859</v>
+        <v>207.901123046875</v>
       </c>
       <c r="C184" t="n">
         <v>211.8699951171875</v>
@@ -5165,7 +5177,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>233.6397857666016</v>
+        <v>233.6397552490234</v>
       </c>
       <c r="C186" t="n">
         <v>238.1000061035156</v>
@@ -5223,7 +5235,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5252,11 +5264,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>237.3980102539062</v>
+        <v>237.3980255126953</v>
       </c>
       <c r="C188" t="n">
         <v>241.9299926757812</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>260.3007507324219</v>
+        <v>260.30078125</v>
       </c>
       <c r="C189" t="n">
         <v>265.2699890136719</v>
@@ -5310,11 +5322,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>266.1392822265625</v>
+        <v>266.1393127441406</v>
       </c>
       <c r="C190" t="n">
         <v>271.2200012207031</v>
@@ -5339,11 +5351,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>294.0759887695312</v>
+        <v>294.0760498046875</v>
       </c>
       <c r="C191" t="n">
         <v>299.6900024414062</v>
@@ -5368,11 +5380,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>279.6219787597656</v>
+        <v>279.6218872070312</v>
       </c>
       <c r="C192" t="n">
         <v>284.9599914550781</v>
@@ -5397,11 +5409,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>249.3694610595703</v>
+        <v>249.3695220947266</v>
       </c>
       <c r="C193" t="n">
         <v>254.1300048828125</v>
@@ -5426,7 +5438,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>206.5862426757812</v>
+        <v>206.5862274169922</v>
       </c>
       <c r="C195" t="n">
         <v>210.5299987792969</v>
@@ -5484,11 +5496,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>208.3426971435547</v>
+        <v>208.3426818847656</v>
       </c>
       <c r="C196" t="n">
         <v>212.3200073242188</v>
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>172.6441955566406</v>
+        <v>172.6441650390625</v>
       </c>
       <c r="C197" t="n">
         <v>175.9400024414062</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>157.2383117675781</v>
+        <v>157.23828125</v>
       </c>
       <c r="C198" t="n">
         <v>160.2400054931641</v>
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>161.9483642578125</v>
+        <v>161.9483795166016</v>
       </c>
       <c r="C199" t="n">
         <v>165.0399932861328</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>180.5728149414062</v>
+        <v>180.5728302001953</v>
       </c>
       <c r="C200" t="n">
         <v>184.0200042724609</v>
@@ -5629,11 +5641,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>153.1954803466797</v>
+        <v>153.1954650878906</v>
       </c>
       <c r="C201" t="n">
         <v>156.1199951171875</v>
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>141.1454772949219</v>
+        <v>141.1455078125</v>
       </c>
       <c r="C202" t="n">
         <v>143.8399963378906</v>
@@ -5687,7 +5699,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5716,7 +5728,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>130.1062316894531</v>
+        <v>130.1062622070312</v>
       </c>
       <c r="C205" t="n">
         <v>132.5899963378906</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>164.8235015869141</v>
+        <v>164.823486328125</v>
       </c>
       <c r="C206" t="n">
         <v>167.9700012207031</v>
@@ -5803,7 +5815,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5832,11 +5844,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>196.0375671386719</v>
+        <v>196.0376129150391</v>
       </c>
       <c r="C208" t="n">
         <v>199.7799987792969</v>
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>194.6539916992188</v>
+        <v>194.6540222167969</v>
       </c>
       <c r="C209" t="n">
         <v>198.3699951171875</v>
@@ -5890,11 +5902,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>219.1955413818359</v>
+        <v>219.1955108642578</v>
       </c>
       <c r="C210" t="n">
         <v>223.3800048828125</v>
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>207.3025360107422</v>
+        <v>207.3025665283203</v>
       </c>
       <c r="C211" t="n">
         <v>211.2599945068359</v>
@@ -5948,11 +5960,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>220.7949523925781</v>
+        <v>220.7949981689453</v>
       </c>
       <c r="C212" t="n">
         <v>225.0099945068359</v>
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>217.3115081787109</v>
+        <v>217.3114776611328</v>
       </c>
       <c r="C213" t="n">
         <v>221.4600067138672</v>
@@ -6006,7 +6018,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>247.1812133789062</v>
+        <v>247.1812438964844</v>
       </c>
       <c r="C216" t="n">
         <v>251.8999938964844</v>
@@ -6093,11 +6105,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>258.2107543945312</v>
+        <v>258.2106628417969</v>
       </c>
       <c r="C217" t="n">
         <v>263.1400146484375</v>
@@ -6122,11 +6134,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>275.8244323730469</v>
+        <v>275.824462890625</v>
       </c>
       <c r="C218" t="n">
         <v>281.0899963378906</v>
@@ -6151,7 +6163,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6180,11 +6192,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>295.9241638183594</v>
+        <v>295.9241943359375</v>
       </c>
       <c r="C220" t="n">
         <v>301.1799926757812</v>
@@ -6209,7 +6221,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>230.3488464355469</v>
+        <v>230.3488006591797</v>
       </c>
       <c r="C222" t="n">
         <v>234.4400024414062</v>
@@ -6267,11 +6279,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>252.6133880615234</v>
+        <v>252.6133728027344</v>
       </c>
       <c r="C223" t="n">
         <v>257.1000061035156</v>
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>254.6794891357422</v>
+        <v>254.6795501708984</v>
       </c>
       <c r="C224" t="n">
         <v>258.7999877929688</v>
@@ -6325,11 +6337,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>248.8734893798828</v>
+        <v>248.8734588623047</v>
       </c>
       <c r="C225" t="n">
         <v>252.8999938964844</v>
@@ -6354,7 +6366,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6383,11 +6395,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>287.18115234375</v>
+        <v>287.1811828613281</v>
       </c>
       <c r="C227" t="n">
         <v>291.3699951171875</v>
@@ -6412,7 +6424,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6441,7 +6453,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6470,11 +6482,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>337.171875</v>
+        <v>337.1718139648438</v>
       </c>
       <c r="C230" t="n">
         <v>341.7000122070312</v>
@@ -6499,11 +6511,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>293.9029541015625</v>
+        <v>293.9029235839844</v>
       </c>
       <c r="C231" t="n">
         <v>297.8500061035156</v>
@@ -6528,11 +6540,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>264.8037414550781</v>
+        <v>264.8037109375</v>
       </c>
       <c r="C232" t="n">
         <v>268.3599853515625</v>
@@ -6557,11 +6569,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>265.5657653808594</v>
+        <v>265.5657043457031</v>
       </c>
       <c r="C233" t="n">
         <v>268.7099914550781</v>
@@ -6586,7 +6598,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6615,7 +6627,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6644,7 +6656,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6673,7 +6685,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6702,7 +6714,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6731,7 +6743,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6760,11 +6772,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>228.6010437011719</v>
+        <v>228.6010284423828</v>
       </c>
       <c r="C240" t="n">
         <v>230.5399932861328</v>
@@ -6789,7 +6801,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6847,7 +6859,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6876,7 +6888,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6905,7 +6917,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6963,7 +6975,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7050,32 +7062,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>237.5800018310547</v>
+        <v>238.2200012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>215652400</v>
+        <v>226713300</v>
       </c>
       <c r="E250" t="n">
         <v>10.96</v>
       </c>
       <c r="F250" t="n">
-        <v>21.67700746633711</v>
+        <v>21.73540157123204</v>
       </c>
       <c r="G250" t="n">
         <v>823000000</v>
       </c>
       <c r="H250" t="n">
-        <v>195528341506.958</v>
+        <v>196055061004.6387</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2620320777642771</v>
+        <v>0.2754718104495747</v>
       </c>
     </row>
   </sheetData>
@@ -7107,75 +7119,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39569</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39660</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40050</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7211,13 +7223,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39661</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39752</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40142</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7253,13 +7265,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7295,13 +7307,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40050</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7337,13 +7349,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40142</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7379,13 +7391,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7412,7 +7424,7 @@
       <c r="I7" t="n">
         <v>0.16</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K7" t="n">
@@ -7425,13 +7437,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7458,7 +7470,7 @@
       <c r="I8" t="n">
         <v>0.155</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K8" t="n">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40430</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7504,7 +7516,7 @@
       <c r="I9" t="n">
         <v>0.14</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K9" t="n">
@@ -7517,13 +7529,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I10" t="n">
         <v>0.1375</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K10" t="n">
@@ -7563,13 +7575,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7596,7 +7608,7 @@
       <c r="I11" t="n">
         <v>0.1175</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K11" t="n">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I12" t="n">
         <v>0.08499999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="K12" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40792</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I13" t="n">
         <v>0.04999999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40792</v>
       </c>
       <c r="K13" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I14" t="n">
         <v>0.005000000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="K14" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40977</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I15" t="n">
         <v>-0.0225</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40977</v>
       </c>
       <c r="K15" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I16" t="n">
         <v>-0.0575</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="K16" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I17" t="n">
         <v>-0.0675</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="K17" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41241</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I18" t="n">
         <v>-0.4475</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41241</v>
       </c>
       <c r="K18" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I19" t="n">
         <v>-0.475</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="K19" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41418</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I20" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41418</v>
       </c>
       <c r="K20" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I21" t="n">
         <v>-0.4225</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="K21" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41603</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I22" t="n">
         <v>-0.245</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41603</v>
       </c>
       <c r="K22" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41703</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I23" t="n">
         <v>-0.4</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41703</v>
       </c>
       <c r="K23" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I24" t="n">
         <v>-0.44</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="K24" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I25" t="n">
         <v>-0.66</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="K25" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I26" t="n">
         <v>-0.51</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="K26" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I27" t="n">
         <v>-0.42</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="K27" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I28" t="n">
         <v>-0.25</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="K28" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I29" t="n">
         <v>-0.15</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="K29" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I30" t="n">
         <v>-0.13</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="K30" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42436</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I31" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42436</v>
       </c>
       <c r="K31" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I32" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="K32" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I33" t="n">
         <v>0.31</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="K33" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I34" t="n">
         <v>0.3</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="K34" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42800</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I35" t="n">
         <v>0.27</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42800</v>
       </c>
       <c r="K35" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I36" t="n">
         <v>0.2</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="K36" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="K37" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I38" t="n">
         <v>0.009999999999999995</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="K38" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I39" t="n">
         <v>0.17</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="K39" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I40" t="n">
         <v>0.64</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="K40" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I41" t="n">
         <v>1.01</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="K41" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43432</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I42" t="n">
         <v>1.07</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43432</v>
       </c>
       <c r="K42" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I43" t="n">
         <v>1.44</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="K43" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43621</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I44" t="n">
         <v>1.47</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43621</v>
       </c>
       <c r="K44" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I45" t="n">
         <v>1.19</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="K45" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I46" t="n">
         <v>0.9400000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="K46" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43895</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I47" t="n">
         <v>0.2</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43895</v>
       </c>
       <c r="K47" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I48" t="n">
         <v>-0.18</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="K48" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I49" t="n">
         <v>2.56</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="K49" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I50" t="n">
         <v>3.83</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="K50" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44272</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I51" t="n">
         <v>4.380000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44272</v>
       </c>
       <c r="K51" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44349</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I52" t="n">
         <v>4.77</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44349</v>
       </c>
       <c r="K52" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I53" t="n">
         <v>2.48</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="K53" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I54" t="n">
         <v>1.8</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="K54" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I55" t="n">
         <v>1.48</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K55" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I56" t="n">
         <v>1.01</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="K56" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I57" t="n">
         <v>0.5199999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="K57" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I58" t="n">
         <v>0.26</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="K58" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I59" t="n">
         <v>0.21</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="K59" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I60" t="n">
         <v>0.38</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="K60" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I61" t="n">
         <v>1.59</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="K61" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I62" t="n">
         <v>2.63</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="K62" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45357</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I63" t="n">
         <v>4.2</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45357</v>
       </c>
       <c r="K63" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I64" t="n">
         <v>5.56</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="K64" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I65" t="n">
         <v>5.75</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K65" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I66" t="n">
         <v>6.08</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="K66" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I67" t="n">
         <v>6.36</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="K67" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I68" t="n">
         <v>6.39</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="K68" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I69" t="n">
         <v>6.88</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="K69" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I70" t="n">
         <v>7.49</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="K70" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I71" t="n">
         <v>7.8</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="K71" t="n">
@@ -10369,13 +10381,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="I72" t="n">
         <v>8.629999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="K72" t="n">
@@ -10415,13 +10427,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10448,7 +10460,7 @@
       <c r="I73" t="n">
         <v>10.96</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K73" t="n">
@@ -10485,52 +10497,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40050</v>
       </c>
       <c r="C2" t="n">
@@ -10559,10 +10571,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40142</v>
       </c>
       <c r="C3" t="n">
@@ -10591,10 +10603,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40248</v>
       </c>
       <c r="C4" t="n">
@@ -10623,10 +10635,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="C5" t="n">
@@ -10655,10 +10667,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40430</v>
       </c>
       <c r="C6" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="C7" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="C8" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40792</v>
       </c>
       <c r="C9" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="C10" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40977</v>
       </c>
       <c r="C11" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="C12" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="C13" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41241</v>
       </c>
       <c r="C14" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="C15" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41418</v>
       </c>
       <c r="C16" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41516</v>
       </c>
       <c r="C17" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41603</v>
       </c>
       <c r="C18" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41703</v>
       </c>
       <c r="C19" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41789</v>
       </c>
       <c r="C20" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41877</v>
       </c>
       <c r="C21" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="C22" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="C23" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="C24" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="C25" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="C26" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42436</v>
       </c>
       <c r="C27" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="C28" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C29" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42695</v>
       </c>
       <c r="C30" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42800</v>
       </c>
       <c r="C31" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="C32" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="C33" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="C34" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="C35" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="C36" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="C37" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43432</v>
       </c>
       <c r="C38" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="C39" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43621</v>
       </c>
       <c r="C40" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43692</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="C41" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43798</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43803</v>
       </c>
       <c r="C42" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43895</v>
       </c>
       <c r="C43" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43980</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="C44" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44068</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="C45" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="C46" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44270</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44272</v>
       </c>
       <c r="C47" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44343</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44349</v>
       </c>
       <c r="C48" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44433</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="C49" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44532</v>
       </c>
       <c r="C50" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="C51" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="C52" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44797</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44798</v>
       </c>
       <c r="C53" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44894</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="C54" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44992</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="C55" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45076</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C56" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="C57" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45257</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="C58" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45357</v>
       </c>
       <c r="C59" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="C60" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C61" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45623</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45630</v>
       </c>
       <c r="C62" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45721</v>
       </c>
       <c r="C63" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45799</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="C64" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45897</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="C65" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="C66" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46078</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46083</v>
       </c>
       <c r="C67" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="C68" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="C69" t="n">
@@ -12721,12 +12733,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CRM.xlsx
+++ b/salidas/empresas/CRM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>10.07025527954102</v>
+        <v>10.07025623321533</v>
       </c>
       <c r="C2" t="n">
         <v>10.26249980926514</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.549293518066406</v>
+        <v>8.549289703369141</v>
       </c>
       <c r="C3" t="n">
         <v>8.712499618530273</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>8.912362098693848</v>
+        <v>8.912363052368164</v>
       </c>
       <c r="C4" t="n">
         <v>9.082500457763672</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>6.304644107818604</v>
+        <v>6.304643630981445</v>
       </c>
       <c r="C8" t="n">
         <v>6.425000190734863</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>8.458523750305176</v>
+        <v>8.458524703979492</v>
       </c>
       <c r="C9" t="n">
         <v>8.619999885559082</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>8.801969528198242</v>
+        <v>8.801967620849609</v>
       </c>
       <c r="C10" t="n">
         <v>8.970000267028809</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>9.572262763977051</v>
+        <v>9.572261810302734</v>
       </c>
       <c r="C11" t="n">
         <v>9.755000114440918</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>9.567356109619141</v>
+        <v>9.567357063293457</v>
       </c>
       <c r="C12" t="n">
         <v>9.75</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>8.941800117492676</v>
+        <v>8.941797256469727</v>
       </c>
       <c r="C13" t="n">
         <v>9.112500190734863</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>10.75223731994629</v>
+        <v>10.75223827362061</v>
       </c>
       <c r="C14" t="n">
         <v>10.95750045776367</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.60750007629395</v>
+        <v>10.60750293731689</v>
       </c>
       <c r="C15" t="n">
         <v>10.8100004196167</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.50446605682373</v>
+        <v>10.50446510314941</v>
       </c>
       <c r="C16" t="n">
         <v>10.70499992370605</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.30330753326416</v>
+        <v>10.30330944061279</v>
       </c>
       <c r="C17" t="n">
         <v>10.5</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>9.918159484863281</v>
+        <v>9.918160438537598</v>
       </c>
       <c r="C21" t="n">
         <v>10.10750007629395</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>12.58966064453125</v>
+        <v>12.58965873718262</v>
       </c>
       <c r="C22" t="n">
         <v>12.82999992370605</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>13.916823387146</v>
+        <v>13.91682434082031</v>
       </c>
       <c r="C24" t="n">
         <v>14.18249988555908</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.3789119720459</v>
+        <v>15.37891292572021</v>
       </c>
       <c r="C25" t="n">
         <v>15.67249965667725</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>12.73439693450928</v>
+        <v>12.73439788818359</v>
       </c>
       <c r="C26" t="n">
         <v>12.97749996185303</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.65032196044922</v>
+        <v>14.65032386779785</v>
       </c>
       <c r="C27" t="n">
         <v>14.93000030517578</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.36999320983887</v>
+        <v>16.36999130249023</v>
       </c>
       <c r="C29" t="n">
         <v>16.6825008392334</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.73885726928711</v>
+        <v>17.73886299133301</v>
       </c>
       <c r="C30" t="n">
         <v>18.07749938964844</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>15.64876079559326</v>
+        <v>15.64876174926758</v>
       </c>
       <c r="C32" t="n">
         <v>15.94750022888184</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.74265098571777</v>
+        <v>13.74265003204346</v>
       </c>
       <c r="C33" t="n">
         <v>14.00500011444092</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>11.87333583831787</v>
+        <v>11.87333488464355</v>
       </c>
       <c r="C34" t="n">
         <v>12.10000038146973</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.595009326934814</v>
+        <v>7.595008373260498</v>
       </c>
       <c r="C35" t="n">
         <v>7.739999771118164</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.020967960357666</v>
+        <v>7.020967483520508</v>
       </c>
       <c r="C36" t="n">
         <v>7.15500020980835</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.527881145477295</v>
+        <v>6.527882099151611</v>
       </c>
       <c r="C38" t="n">
         <v>6.652500152587891</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.86887264251709</v>
+        <v>6.868872165679932</v>
       </c>
       <c r="C39" t="n">
         <v>7</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.029220581054688</v>
+        <v>8.029221534729004</v>
       </c>
       <c r="C40" t="n">
         <v>8.182499885559082</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.50201416015625</v>
+        <v>10.50201606750488</v>
       </c>
       <c r="C41" t="n">
         <v>10.70250034332275</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>9.363743782043457</v>
+        <v>9.363744735717773</v>
       </c>
       <c r="C43" t="n">
         <v>9.542499542236328</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>10.63203144073486</v>
+        <v>10.63203239440918</v>
       </c>
       <c r="C44" t="n">
         <v>10.83500003814697</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.96588802337646</v>
+        <v>13.96588897705078</v>
       </c>
       <c r="C46" t="n">
         <v>14.23250007629395</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.92173004150391</v>
+        <v>13.92173290252686</v>
       </c>
       <c r="C47" t="n">
         <v>14.1875</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.3764591217041</v>
+        <v>15.37646102905273</v>
       </c>
       <c r="C48" t="n">
         <v>15.67000007629395</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>18.09702491760254</v>
+        <v>18.09702301025391</v>
       </c>
       <c r="C49" t="n">
         <v>18.4424991607666</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.58988761901855</v>
+        <v>15.58988380432129</v>
       </c>
       <c r="C50" t="n">
         <v>15.88749980926514</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>18.26383590698242</v>
+        <v>18.26383781433105</v>
       </c>
       <c r="C52" t="n">
         <v>18.61249923706055</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>20.99912071228027</v>
+        <v>20.99912261962891</v>
       </c>
       <c r="C53" t="n">
         <v>21.39999961853027</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>21.22726821899414</v>
+        <v>21.22726631164551</v>
       </c>
       <c r="C54" t="n">
         <v>21.63249969482422</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.05309295654297</v>
+        <v>21.05309104919434</v>
       </c>
       <c r="C55" t="n">
         <v>21.45499992370605</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.27410316467285</v>
+        <v>24.27410125732422</v>
       </c>
       <c r="C56" t="n">
         <v>24.73749923706055</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>28.47393035888672</v>
+        <v>28.47392654418945</v>
       </c>
       <c r="C59" t="n">
         <v>29.01749992370605</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>34.15301895141602</v>
+        <v>34.15301132202148</v>
       </c>
       <c r="C60" t="n">
         <v>34.80500030517578</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>32.3818244934082</v>
+        <v>32.38182830810547</v>
       </c>
       <c r="C61" t="n">
         <v>33</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>31.68021583557129</v>
+        <v>31.68021965026855</v>
       </c>
       <c r="C62" t="n">
         <v>32.28499984741211</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>32.44805908203125</v>
+        <v>32.44805526733398</v>
       </c>
       <c r="C63" t="n">
         <v>33.06750106811523</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>34.00092315673828</v>
+        <v>34.00091552734375</v>
       </c>
       <c r="C65" t="n">
         <v>34.65000152587891</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>37.35193634033203</v>
+        <v>37.3519401550293</v>
       </c>
       <c r="C66" t="n">
         <v>38.06499862670898</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>36.54730987548828</v>
+        <v>36.54729843139648</v>
       </c>
       <c r="C67" t="n">
         <v>37.24499893188477</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>35.49980545043945</v>
+        <v>35.49980163574219</v>
       </c>
       <c r="C68" t="n">
         <v>36.1775016784668</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.58453750610352</v>
+        <v>31.58454513549805</v>
       </c>
       <c r="C69" t="n">
         <v>32.1875</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>28.03481101989746</v>
+        <v>28.03480529785156</v>
       </c>
       <c r="C70" t="n">
         <v>28.56999969482422</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.66884231567383</v>
+        <v>32.66884613037109</v>
       </c>
       <c r="C71" t="n">
         <v>33.29249954223633</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>29.05042266845703</v>
+        <v>29.05042457580566</v>
       </c>
       <c r="C72" t="n">
         <v>29.60499954223633</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.65301132202148</v>
+        <v>28.65300750732422</v>
       </c>
       <c r="C74" t="n">
         <v>29.20000076293945</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>35.11955261230469</v>
+        <v>35.11955642700195</v>
       </c>
       <c r="C75" t="n">
         <v>35.79000091552734</v>
@@ -2219,7 +2219,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>33.91751098632812</v>
+        <v>33.91750335693359</v>
       </c>
       <c r="C79" t="n">
         <v>34.56499862670898</v>
@@ -2246,7 +2246,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>30.50760459899902</v>
+        <v>30.50760269165039</v>
       </c>
       <c r="C80" t="n">
         <v>31.09000015258789</v>
@@ -2273,7 +2273,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>35.61509704589844</v>
+        <v>35.6151008605957</v>
       </c>
       <c r="C81" t="n">
         <v>36.29499816894531</v>
@@ -2300,7 +2300,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>37.45743560791016</v>
+        <v>37.45743179321289</v>
       </c>
       <c r="C82" t="n">
         <v>38.17250061035156</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>35.81135177612305</v>
+        <v>35.81134796142578</v>
       </c>
       <c r="C83" t="n">
         <v>36.49499893188477</v>
@@ -2408,7 +2408,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>42.22639465332031</v>
+        <v>42.22639083862305</v>
       </c>
       <c r="C86" t="n">
         <v>43.03250122070312</v>
@@ -2435,7 +2435,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.51251220703125</v>
+        <v>41.51252365112305</v>
       </c>
       <c r="C87" t="n">
         <v>42.30500030517578</v>
@@ -2462,7 +2462,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.87001037597656</v>
+        <v>43.87001800537109</v>
       </c>
       <c r="C88" t="n">
         <v>44.70750045776367</v>
@@ -2489,7 +2489,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>40.33990097045898</v>
+        <v>40.33990478515625</v>
       </c>
       <c r="C89" t="n">
         <v>41.11000061035156</v>
@@ -2516,7 +2516,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>41.53705215454102</v>
+        <v>41.53704833984375</v>
       </c>
       <c r="C90" t="n">
         <v>42.33000183105469</v>
@@ -2543,7 +2543,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>37.46479034423828</v>
+        <v>37.46478271484375</v>
       </c>
       <c r="C91" t="n">
         <v>38.18000030517578</v>
@@ -2570,7 +2570,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.93044662475586</v>
+        <v>42.93045425415039</v>
       </c>
       <c r="C92" t="n">
         <v>43.75</v>
@@ -2597,7 +2597,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.20966339111328</v>
+        <v>48.20967102050781</v>
       </c>
       <c r="C93" t="n">
         <v>49.13000106811523</v>
@@ -2624,7 +2624,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>50.93758773803711</v>
+        <v>50.93759155273438</v>
       </c>
       <c r="C94" t="n">
         <v>51.90999984741211</v>
@@ -2651,7 +2651,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>52.36042404174805</v>
+        <v>52.36042785644531</v>
       </c>
       <c r="C95" t="n">
         <v>53.36000061035156</v>
@@ -2678,7 +2678,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>51.11421585083008</v>
+        <v>51.11421966552734</v>
       </c>
       <c r="C96" t="n">
         <v>52.09000015258789</v>
@@ -2732,7 +2732,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>59.39611434936523</v>
+        <v>59.39611053466797</v>
       </c>
       <c r="C98" t="n">
         <v>60.52999877929688</v>
@@ -2786,7 +2786,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>56.02054977416992</v>
+        <v>56.02055358886719</v>
       </c>
       <c r="C100" t="n">
         <v>57.09000015258789</v>
@@ -2813,7 +2813,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>50.68246078491211</v>
+        <v>50.68246841430664</v>
       </c>
       <c r="C101" t="n">
         <v>51.65000152587891</v>
@@ -2840,7 +2840,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>51.64410400390625</v>
+        <v>51.64411163330078</v>
       </c>
       <c r="C102" t="n">
         <v>52.63000106811523</v>
@@ -2867,7 +2867,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.99200439453125</v>
+        <v>56.99201202392578</v>
       </c>
       <c r="C103" t="n">
         <v>58.08000183105469</v>
@@ -2921,7 +2921,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>57.98309326171875</v>
+        <v>57.98308563232422</v>
       </c>
       <c r="C105" t="n">
         <v>59.09000015258789</v>
@@ -2948,7 +2948,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>56.45230865478516</v>
+        <v>56.45231246948242</v>
       </c>
       <c r="C106" t="n">
         <v>57.52999877929688</v>
@@ -2975,7 +2975,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>62.79130172729492</v>
+        <v>62.79130554199219</v>
       </c>
       <c r="C107" t="n">
         <v>63.9900016784668</v>
@@ -3002,7 +3002,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>58.74847793579102</v>
+        <v>58.74847030639648</v>
       </c>
       <c r="C108" t="n">
         <v>59.86999893188477</v>
@@ -3029,7 +3029,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>58.19897079467773</v>
+        <v>58.198974609375</v>
       </c>
       <c r="C109" t="n">
         <v>59.31000137329102</v>
@@ -3056,7 +3056,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>55.39255142211914</v>
+        <v>55.39254760742188</v>
       </c>
       <c r="C110" t="n">
         <v>56.45000076293945</v>
@@ -3083,7 +3083,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>68.080322265625</v>
+        <v>68.08032989501953</v>
       </c>
       <c r="C111" t="n">
         <v>69.37999725341797</v>
@@ -3137,7 +3137,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>71.45590209960938</v>
+        <v>71.45589447021484</v>
       </c>
       <c r="C113" t="n">
         <v>72.81999969482422</v>
@@ -3164,7 +3164,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>71.38719940185547</v>
+        <v>71.38720703125</v>
       </c>
       <c r="C114" t="n">
         <v>72.75</v>
@@ -3245,7 +3245,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>68.06069946289062</v>
+        <v>68.06072235107422</v>
       </c>
       <c r="C117" t="n">
         <v>69.36000061035156</v>
@@ -3272,7 +3272,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>68.12940979003906</v>
+        <v>68.12939453125</v>
       </c>
       <c r="C118" t="n">
         <v>69.43000030517578</v>
@@ -3299,7 +3299,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>76.25429534912109</v>
+        <v>76.25428771972656</v>
       </c>
       <c r="C119" t="n">
         <v>77.70999908447266</v>
@@ -3326,7 +3326,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>78.19721221923828</v>
+        <v>78.19719696044922</v>
       </c>
       <c r="C120" t="n">
         <v>79.69000244140625</v>
@@ -3353,7 +3353,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>76.93137359619141</v>
+        <v>76.93136596679688</v>
       </c>
       <c r="C121" t="n">
         <v>78.40000152587891</v>
@@ -3380,7 +3380,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>66.78505706787109</v>
+        <v>66.78504943847656</v>
       </c>
       <c r="C122" t="n">
         <v>68.05999755859375</v>
@@ -3407,7 +3407,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>66.48087310791016</v>
+        <v>66.48086547851562</v>
       </c>
       <c r="C123" t="n">
         <v>67.75</v>
@@ -3434,7 +3434,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>72.44696807861328</v>
+        <v>72.44698333740234</v>
       </c>
       <c r="C124" t="n">
         <v>73.83000183105469</v>
@@ -3461,7 +3461,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>74.38007354736328</v>
+        <v>74.38006591796875</v>
       </c>
       <c r="C125" t="n">
         <v>75.80000305175781</v>
@@ -3515,7 +3515,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>77.92245483398438</v>
+        <v>77.92243194580078</v>
       </c>
       <c r="C127" t="n">
         <v>79.41000366210938</v>
@@ -3596,7 +3596,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>69.99378967285156</v>
+        <v>69.99380493164062</v>
       </c>
       <c r="C130" t="n">
         <v>71.33000183105469</v>
@@ -3625,7 +3625,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>73.75205993652344</v>
+        <v>73.75205230712891</v>
       </c>
       <c r="C131" t="n">
         <v>75.16000366210938</v>
@@ -3654,7 +3654,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>70.65126037597656</v>
+        <v>70.65125274658203</v>
       </c>
       <c r="C132" t="n">
         <v>72</v>
@@ -3683,7 +3683,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>67.17755889892578</v>
+        <v>67.17756652832031</v>
       </c>
       <c r="C133" t="n">
         <v>68.45999908447266</v>
@@ -3712,7 +3712,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>77.61824798583984</v>
+        <v>77.61824035644531</v>
       </c>
       <c r="C134" t="n">
         <v>79.09999847412109</v>
@@ -3741,7 +3741,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>79.82611083984375</v>
+        <v>79.82608795166016</v>
       </c>
       <c r="C135" t="n">
         <v>81.34999847412109</v>
@@ -3770,7 +3770,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>80.94473266601562</v>
+        <v>80.94474792480469</v>
       </c>
       <c r="C136" t="n">
         <v>82.48999786376953</v>
@@ -3828,7 +3828,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>87.96080780029297</v>
+        <v>87.9608154296875</v>
       </c>
       <c r="C138" t="n">
         <v>89.63999938964844</v>
@@ -3886,7 +3886,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>89.09907531738281</v>
+        <v>89.09908294677734</v>
       </c>
       <c r="C140" t="n">
         <v>90.80000305175781</v>
@@ -3915,7 +3915,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>93.70122528076172</v>
+        <v>93.70123291015625</v>
       </c>
       <c r="C141" t="n">
         <v>95.48999786376953</v>
@@ -3969,7 +3969,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>100.4228973388672</v>
+        <v>100.4228897094727</v>
       </c>
       <c r="C143" t="n">
         <v>102.3399963378906</v>
@@ -3996,7 +3996,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>102.3658218383789</v>
+        <v>102.3658142089844</v>
       </c>
       <c r="C144" t="n">
         <v>104.3199996948242</v>
@@ -4025,7 +4025,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>100.3149719238281</v>
+        <v>100.3149795532227</v>
       </c>
       <c r="C145" t="n">
         <v>102.2300033569336</v>
@@ -4141,7 +4141,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>118.7235412597656</v>
+        <v>118.7235336303711</v>
       </c>
       <c r="C149" t="n">
         <v>120.9899978637695</v>
@@ -4170,7 +4170,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>126.9073028564453</v>
+        <v>126.9073104858398</v>
       </c>
       <c r="C150" t="n">
         <v>129.3300018310547</v>
@@ -4199,7 +4199,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>133.8448638916016</v>
+        <v>133.8448486328125</v>
       </c>
       <c r="C151" t="n">
         <v>136.3999938964844</v>
@@ -4228,7 +4228,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>134.5808258056641</v>
+        <v>134.580810546875</v>
       </c>
       <c r="C152" t="n">
         <v>137.1499938964844</v>
@@ -4257,7 +4257,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>149.8199005126953</v>
+        <v>149.8199157714844</v>
       </c>
       <c r="C153" t="n">
         <v>152.6799926757812</v>
@@ -4344,7 +4344,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>140.0857543945312</v>
+        <v>140.0857238769531</v>
       </c>
       <c r="C156" t="n">
         <v>142.7599945068359</v>
@@ -4402,7 +4402,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>149.1231994628906</v>
+        <v>149.1232299804688</v>
       </c>
       <c r="C158" t="n">
         <v>151.9700012207031</v>
@@ -4431,7 +4431,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>160.5843963623047</v>
+        <v>160.5844116210938</v>
       </c>
       <c r="C159" t="n">
         <v>163.6499938964844</v>
@@ -4489,7 +4489,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>162.2525787353516</v>
+        <v>162.2525634765625</v>
       </c>
       <c r="C161" t="n">
         <v>165.3500061035156</v>
@@ -4547,7 +4547,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>148.8876953125</v>
+        <v>148.8876800537109</v>
       </c>
       <c r="C163" t="n">
         <v>151.7299957275391</v>
@@ -4634,7 +4634,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>145.6593475341797</v>
+        <v>145.6593627929688</v>
       </c>
       <c r="C166" t="n">
         <v>148.4400024414062</v>
@@ -4663,7 +4663,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>153.5585327148438</v>
+        <v>153.5585632324219</v>
       </c>
       <c r="C167" t="n">
         <v>156.4900054931641</v>
@@ -4692,7 +4692,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>159.8386535644531</v>
+        <v>159.8386383056641</v>
       </c>
       <c r="C168" t="n">
         <v>162.8899993896484</v>
@@ -4721,7 +4721,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>159.5933074951172</v>
+        <v>159.5933532714844</v>
       </c>
       <c r="C169" t="n">
         <v>162.6399993896484</v>
@@ -4779,7 +4779,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>167.2079315185547</v>
+        <v>167.2080078125</v>
       </c>
       <c r="C171" t="n">
         <v>170.3999938964844</v>
@@ -4808,7 +4808,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>141.2828674316406</v>
+        <v>141.2828826904297</v>
       </c>
       <c r="C172" t="n">
         <v>143.9799957275391</v>
@@ -4866,7 +4866,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>171.5157318115234</v>
+        <v>171.5157012939453</v>
       </c>
       <c r="C174" t="n">
         <v>174.7899932861328</v>
@@ -4949,7 +4949,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>267.5425109863281</v>
+        <v>267.5425720214844</v>
       </c>
       <c r="C177" t="n">
         <v>272.6499938964844</v>
@@ -4978,7 +4978,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>246.6121215820312</v>
+        <v>246.6121063232422</v>
       </c>
       <c r="C178" t="n">
         <v>251.3200073242188</v>
@@ -5036,7 +5036,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>241.1955261230469</v>
+        <v>241.1955413818359</v>
       </c>
       <c r="C180" t="n">
         <v>245.8000030517578</v>
@@ -5065,7 +5065,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>218.3614196777344</v>
+        <v>218.3614349365234</v>
       </c>
       <c r="C181" t="n">
         <v>222.5299987792969</v>
@@ -5094,7 +5094,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.3347015380859</v>
+        <v>221.3346862792969</v>
       </c>
       <c r="C182" t="n">
         <v>225.5599975585938</v>
@@ -5123,7 +5123,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>212.4443969726562</v>
+        <v>212.4443817138672</v>
       </c>
       <c r="C183" t="n">
         <v>216.5</v>
@@ -5152,7 +5152,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>207.901123046875</v>
+        <v>207.9011077880859</v>
       </c>
       <c r="C184" t="n">
         <v>211.8699951171875</v>
@@ -5181,7 +5181,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>226.0054931640625</v>
+        <v>226.0055389404297</v>
       </c>
       <c r="C185" t="n">
         <v>230.3200073242188</v>
@@ -5210,7 +5210,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>233.6397552490234</v>
+        <v>233.6397705078125</v>
       </c>
       <c r="C186" t="n">
         <v>238.1000061035156</v>
@@ -5239,7 +5239,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>239.6941986083984</v>
+        <v>239.6942291259766</v>
       </c>
       <c r="C187" t="n">
         <v>244.2700042724609</v>
@@ -5297,7 +5297,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>260.30078125</v>
+        <v>260.3008117675781</v>
       </c>
       <c r="C189" t="n">
         <v>265.2699890136719</v>
@@ -5355,7 +5355,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>294.0760498046875</v>
+        <v>294.0759887695312</v>
       </c>
       <c r="C191" t="n">
         <v>299.6900024414062</v>
@@ -5384,7 +5384,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>279.6218872070312</v>
+        <v>279.6219482421875</v>
       </c>
       <c r="C192" t="n">
         <v>284.9599914550781</v>
@@ -5413,7 +5413,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>249.3695220947266</v>
+        <v>249.3694458007812</v>
       </c>
       <c r="C193" t="n">
         <v>254.1300048828125</v>
@@ -5471,7 +5471,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>206.5862274169922</v>
+        <v>206.5862426757812</v>
       </c>
       <c r="C195" t="n">
         <v>210.5299987792969</v>
@@ -5500,7 +5500,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>208.3426818847656</v>
+        <v>208.3427276611328</v>
       </c>
       <c r="C196" t="n">
         <v>212.3200073242188</v>
@@ -5529,7 +5529,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>172.6441650390625</v>
+        <v>172.6441955566406</v>
       </c>
       <c r="C197" t="n">
         <v>175.9400024414062</v>
@@ -5587,7 +5587,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>161.9483795166016</v>
+        <v>161.9483642578125</v>
       </c>
       <c r="C199" t="n">
         <v>165.0399932861328</v>
@@ -5616,7 +5616,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>180.5728302001953</v>
+        <v>180.5728149414062</v>
       </c>
       <c r="C200" t="n">
         <v>184.0200042724609</v>
@@ -5645,7 +5645,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>153.1954650878906</v>
+        <v>153.1954498291016</v>
       </c>
       <c r="C201" t="n">
         <v>156.1199951171875</v>
@@ -5703,7 +5703,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>159.5442504882812</v>
+        <v>159.5442810058594</v>
       </c>
       <c r="C203" t="n">
         <v>162.5899963378906</v>
@@ -5732,7 +5732,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>157.2480926513672</v>
+        <v>157.2480773925781</v>
       </c>
       <c r="C204" t="n">
         <v>160.25</v>
@@ -5761,7 +5761,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>130.1062622070312</v>
+        <v>130.1062469482422</v>
       </c>
       <c r="C205" t="n">
         <v>132.5899963378906</v>
@@ -5790,7 +5790,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>164.823486328125</v>
+        <v>164.8235321044922</v>
       </c>
       <c r="C206" t="n">
         <v>167.9700012207031</v>
@@ -5819,7 +5819,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>160.545166015625</v>
+        <v>160.5451507568359</v>
       </c>
       <c r="C207" t="n">
         <v>163.6100006103516</v>
@@ -5848,7 +5848,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>196.0376129150391</v>
+        <v>196.0375823974609</v>
       </c>
       <c r="C208" t="n">
         <v>199.7799987792969</v>
@@ -5877,7 +5877,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>194.6540222167969</v>
+        <v>194.6540069580078</v>
       </c>
       <c r="C209" t="n">
         <v>198.3699951171875</v>
@@ -5906,7 +5906,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>219.1955108642578</v>
+        <v>219.1955261230469</v>
       </c>
       <c r="C210" t="n">
         <v>223.3800048828125</v>
@@ -5935,7 +5935,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>207.3025665283203</v>
+        <v>207.3025207519531</v>
       </c>
       <c r="C211" t="n">
         <v>211.2599945068359</v>
@@ -5964,7 +5964,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>220.7949981689453</v>
+        <v>220.7949829101562</v>
       </c>
       <c r="C212" t="n">
         <v>225.0099945068359</v>
@@ -5993,7 +5993,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>217.3114776611328</v>
+        <v>217.3114929199219</v>
       </c>
       <c r="C213" t="n">
         <v>221.4600067138672</v>
@@ -6022,7 +6022,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>198.9813995361328</v>
+        <v>198.9813690185547</v>
       </c>
       <c r="C214" t="n">
         <v>202.7799987792969</v>
@@ -6080,7 +6080,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>247.1812438964844</v>
+        <v>247.1812591552734</v>
       </c>
       <c r="C216" t="n">
         <v>251.8999938964844</v>
@@ -6109,7 +6109,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>258.2106628417969</v>
+        <v>258.2107543945312</v>
       </c>
       <c r="C217" t="n">
         <v>263.1400146484375</v>
@@ -6138,7 +6138,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>275.824462890625</v>
+        <v>275.8244323730469</v>
       </c>
       <c r="C218" t="n">
         <v>281.0899963378906</v>
@@ -6167,7 +6167,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>303.0350036621094</v>
+        <v>303.0350341796875</v>
       </c>
       <c r="C219" t="n">
         <v>308.8200073242188</v>
@@ -6196,7 +6196,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>295.9241943359375</v>
+        <v>295.9241333007812</v>
       </c>
       <c r="C220" t="n">
         <v>301.1799926757812</v>
@@ -6225,7 +6225,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>264.2467956542969</v>
+        <v>264.2467651367188</v>
       </c>
       <c r="C221" t="n">
         <v>268.9400024414062</v>
@@ -6254,7 +6254,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>230.3488006591797</v>
+        <v>230.3488464355469</v>
       </c>
       <c r="C222" t="n">
         <v>234.4400024414062</v>
@@ -6283,7 +6283,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>252.6133728027344</v>
+        <v>252.6133575439453</v>
       </c>
       <c r="C223" t="n">
         <v>257.1000061035156</v>
@@ -6312,7 +6312,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>254.6795501708984</v>
+        <v>254.6795196533203</v>
       </c>
       <c r="C224" t="n">
         <v>258.7999877929688</v>
@@ -6341,7 +6341,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>248.8734588623047</v>
+        <v>248.8734893798828</v>
       </c>
       <c r="C225" t="n">
         <v>252.8999938964844</v>
@@ -6399,7 +6399,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>287.1811828613281</v>
+        <v>287.18115234375</v>
       </c>
       <c r="C227" t="n">
         <v>291.3699951171875</v>
@@ -6428,7 +6428,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>325.2459106445312</v>
+        <v>325.2459411621094</v>
       </c>
       <c r="C228" t="n">
         <v>329.989990234375</v>
@@ -6486,7 +6486,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>337.1718139648438</v>
+        <v>337.171875</v>
       </c>
       <c r="C230" t="n">
         <v>341.7000122070312</v>
@@ -6515,7 +6515,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>293.9029235839844</v>
+        <v>293.9029541015625</v>
       </c>
       <c r="C231" t="n">
         <v>297.8500061035156</v>
@@ -6544,7 +6544,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>264.8037109375</v>
+        <v>264.8037719726562</v>
       </c>
       <c r="C232" t="n">
         <v>268.3599853515625</v>
@@ -6573,7 +6573,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>265.5657043457031</v>
+        <v>265.5657348632812</v>
       </c>
       <c r="C233" t="n">
         <v>268.7099914550781</v>
@@ -6602,7 +6602,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>262.2648010253906</v>
+        <v>262.2648315429688</v>
       </c>
       <c r="C234" t="n">
         <v>265.3699951171875</v>
@@ -6660,7 +6660,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>255.7120056152344</v>
+        <v>255.7120361328125</v>
       </c>
       <c r="C236" t="n">
         <v>258.3299865722656</v>
